--- a/education_forms/026_enrollment_verification_form--education_forms.xlsx
+++ b/education_forms/026_enrollment_verification_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1564,17 +1564,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>enrollment_type_choices</t>
+          <t>student_category_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>graduated</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>On Hold</t>
+          <t>Graduated</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>graduated</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Graduated</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -1654,29 +1654,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>withdrawn</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>student_category_choices</t>
+          <t>enrollment_category_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>graduated</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>On Hold</t>
+          <t>Graduated</t>
         </is>
       </c>
     </row>
@@ -1739,29 +1739,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>graduated</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Graduated</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>enrollment_category_choices</t>
+          <t>school_category_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1807,29 +1807,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>school_category_choices</t>
+          <t>school_subcategory_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1875,29 +1875,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>school_subcategory_choices</t>
+          <t>student_subcategory_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>graduated</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>On Hold</t>
+          <t>Graduated</t>
         </is>
       </c>
     </row>
@@ -1960,27 +1960,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>graduated</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Graduated</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>student_subcategory_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
